--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -4535,10 +4535,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119764988</v>
+        <v>119765224</v>
       </c>
       <c r="B34" t="n">
-        <v>91858</v>
+        <v>57463</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4551,24 +4551,33 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4368</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Åberga, Åberga, Dlr</t>
@@ -4581,7 +4590,7 @@
         <v>6779884</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4610,7 +4619,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4620,7 +4629,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4759,10 +4768,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119765224</v>
+        <v>119764988</v>
       </c>
       <c r="B36" t="n">
-        <v>57463</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4775,33 +4784,24 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>4368</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Åberga, Åberga, Dlr</t>
@@ -4814,7 +4814,7 @@
         <v>6779884</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -4535,10 +4535,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119765224</v>
+        <v>119765573</v>
       </c>
       <c r="B34" t="n">
-        <v>57463</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4551,46 +4551,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>4368</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Åberga, Åberga, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486838</v>
+        <v>486800</v>
       </c>
       <c r="R34" t="n">
-        <v>6779884</v>
+        <v>6779911</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4619,7 +4610,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4629,7 +4620,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4656,10 +4647,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119765573</v>
+        <v>119765224</v>
       </c>
       <c r="B35" t="n">
-        <v>91858</v>
+        <v>57463</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4672,37 +4663,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4368</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Åberga, Åberga, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486800</v>
+        <v>486838</v>
       </c>
       <c r="R35" t="n">
-        <v>6779911</v>
+        <v>6779884</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -4647,10 +4647,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119765224</v>
+        <v>119764988</v>
       </c>
       <c r="B35" t="n">
-        <v>57463</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4663,33 +4663,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>4368</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Åberga, Åberga, Dlr</t>
@@ -4702,7 +4693,7 @@
         <v>6779884</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4731,7 +4722,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4741,7 +4732,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4768,10 +4759,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119764988</v>
+        <v>119765224</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>57463</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4784,24 +4775,33 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4368</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Åberga, Åberga, Dlr</t>
@@ -4814,7 +4814,7 @@
         <v>6779884</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -4535,10 +4535,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119765573</v>
+        <v>119764988</v>
       </c>
       <c r="B34" t="n">
-        <v>91858</v>
+        <v>91876</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4575,13 +4575,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486800</v>
+        <v>486838</v>
       </c>
       <c r="R34" t="n">
-        <v>6779911</v>
+        <v>6779884</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4647,10 +4647,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119764988</v>
+        <v>119765224</v>
       </c>
       <c r="B35" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4663,24 +4663,33 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4368</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Åberga, Åberga, Dlr</t>
@@ -4693,7 +4702,7 @@
         <v>6779884</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4722,7 +4731,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4732,7 +4741,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4759,10 +4768,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119765224</v>
+        <v>119765573</v>
       </c>
       <c r="B36" t="n">
-        <v>57463</v>
+        <v>91876</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4775,46 +4784,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>4368</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Åberga, Åberga, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486838</v>
+        <v>486800</v>
       </c>
       <c r="R36" t="n">
-        <v>6779884</v>
+        <v>6779911</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4883,7 +4883,7 @@
         <v>119905244</v>
       </c>
       <c r="B37" t="n">
-        <v>91858</v>
+        <v>91876</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>119905347</v>
       </c>
       <c r="B38" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -4535,7 +4535,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119764988</v>
+        <v>119765573</v>
       </c>
       <c r="B34" t="n">
         <v>91876</v>
@@ -4575,13 +4575,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486838</v>
+        <v>486800</v>
       </c>
       <c r="R34" t="n">
-        <v>6779884</v>
+        <v>6779911</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4768,7 +4768,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119765573</v>
+        <v>119764988</v>
       </c>
       <c r="B36" t="n">
         <v>91876</v>
@@ -4808,13 +4808,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486800</v>
+        <v>486838</v>
       </c>
       <c r="R36" t="n">
-        <v>6779911</v>
+        <v>6779884</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>119368675</v>
       </c>
       <c r="B28" t="n">
-        <v>90232</v>
+        <v>90242</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>119368675</v>
       </c>
       <c r="B28" t="n">
-        <v>90242</v>
+        <v>90254</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5106,6 +5106,330 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121560193</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92013</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mickelvål, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>486772</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6779917</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Flera mycel i området</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121560204</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90737</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mickelvål, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>486791</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6779833</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121560208</v>
+      </c>
+      <c r="B41" t="n">
+        <v>94506</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mickelvål, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>486785</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6779823</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -5108,10 +5108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121560193</v>
+        <v>121560208</v>
       </c>
       <c r="B39" t="n">
-        <v>92013</v>
+        <v>94506</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5120,30 +5120,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4368</v>
+        <v>2809</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5151,10 +5152,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486772</v>
+        <v>486785</v>
       </c>
       <c r="R39" t="n">
-        <v>6779917</v>
+        <v>6779823</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5187,11 +5188,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5325,10 +5321,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121560208</v>
+        <v>121560193</v>
       </c>
       <c r="B41" t="n">
-        <v>94506</v>
+        <v>92013</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5337,31 +5333,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2809</v>
+        <v>4368</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5369,10 +5364,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486785</v>
+        <v>486772</v>
       </c>
       <c r="R41" t="n">
-        <v>6779823</v>
+        <v>6779917</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5405,6 +5400,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -5108,10 +5108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121560208</v>
+        <v>121560193</v>
       </c>
       <c r="B39" t="n">
-        <v>94506</v>
+        <v>92014</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5120,31 +5120,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2809</v>
+        <v>4368</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5152,10 +5151,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486785</v>
+        <v>486772</v>
       </c>
       <c r="R39" t="n">
-        <v>6779823</v>
+        <v>6779917</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5188,6 +5187,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5218,7 +5222,7 @@
         <v>121560204</v>
       </c>
       <c r="B40" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5321,10 +5325,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121560193</v>
+        <v>121560208</v>
       </c>
       <c r="B41" t="n">
-        <v>92013</v>
+        <v>94507</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5333,30 +5337,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4368</v>
+        <v>2809</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5364,10 +5369,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486772</v>
+        <v>486785</v>
       </c>
       <c r="R41" t="n">
-        <v>6779917</v>
+        <v>6779823</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5400,11 +5405,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -5108,10 +5108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121560193</v>
+        <v>121560204</v>
       </c>
       <c r="B39" t="n">
-        <v>92014</v>
+        <v>90738</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5124,21 +5124,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4368</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486772</v>
+        <v>486791</v>
       </c>
       <c r="R39" t="n">
-        <v>6779917</v>
+        <v>6779833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5187,11 +5187,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5219,10 +5214,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121560204</v>
+        <v>121560193</v>
       </c>
       <c r="B40" t="n">
-        <v>90738</v>
+        <v>92014</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5235,21 +5230,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5262,10 +5257,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486791</v>
+        <v>486772</v>
       </c>
       <c r="R40" t="n">
-        <v>6779833</v>
+        <v>6779917</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5298,6 +5293,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -5108,10 +5108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121560204</v>
+        <v>121560208</v>
       </c>
       <c r="B39" t="n">
-        <v>90738</v>
+        <v>94507</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5120,30 +5120,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5151,10 +5152,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486791</v>
+        <v>486785</v>
       </c>
       <c r="R39" t="n">
-        <v>6779833</v>
+        <v>6779823</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5214,10 +5215,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121560193</v>
+        <v>121560204</v>
       </c>
       <c r="B40" t="n">
-        <v>92014</v>
+        <v>90738</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5230,21 +5231,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4368</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5257,10 +5258,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486772</v>
+        <v>486791</v>
       </c>
       <c r="R40" t="n">
-        <v>6779917</v>
+        <v>6779833</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5293,11 +5294,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5325,10 +5321,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121560208</v>
+        <v>121560193</v>
       </c>
       <c r="B41" t="n">
-        <v>94507</v>
+        <v>92014</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5337,31 +5333,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2809</v>
+        <v>4368</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5369,10 +5364,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486785</v>
+        <v>486772</v>
       </c>
       <c r="R41" t="n">
-        <v>6779823</v>
+        <v>6779917</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5405,6 +5400,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -5108,10 +5108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121560193</v>
+        <v>121560204</v>
       </c>
       <c r="B39" t="n">
-        <v>92022</v>
+        <v>90746</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5124,21 +5124,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4368</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486772</v>
+        <v>486791</v>
       </c>
       <c r="R39" t="n">
-        <v>6779917</v>
+        <v>6779833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5187,11 +5187,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5219,10 +5214,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121560208</v>
+        <v>121560193</v>
       </c>
       <c r="B40" t="n">
-        <v>94515</v>
+        <v>92022</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5231,31 +5226,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2809</v>
+        <v>4368</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5263,10 +5257,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486785</v>
+        <v>486772</v>
       </c>
       <c r="R40" t="n">
-        <v>6779823</v>
+        <v>6779917</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5299,6 +5293,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5326,10 +5325,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121560204</v>
+        <v>121560208</v>
       </c>
       <c r="B41" t="n">
-        <v>90746</v>
+        <v>94515</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5338,30 +5337,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486791</v>
+        <v>486785</v>
       </c>
       <c r="R41" t="n">
-        <v>6779833</v>
+        <v>6779823</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -5108,10 +5108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121560204</v>
+        <v>121560193</v>
       </c>
       <c r="B39" t="n">
-        <v>90746</v>
+        <v>92022</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5124,21 +5124,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486791</v>
+        <v>486772</v>
       </c>
       <c r="R39" t="n">
-        <v>6779833</v>
+        <v>6779917</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5187,6 +5187,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5214,10 +5219,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121560193</v>
+        <v>121560208</v>
       </c>
       <c r="B40" t="n">
-        <v>92022</v>
+        <v>94515</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5226,30 +5231,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4368</v>
+        <v>2809</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5257,10 +5263,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486772</v>
+        <v>486785</v>
       </c>
       <c r="R40" t="n">
-        <v>6779917</v>
+        <v>6779823</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5293,11 +5299,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5325,10 +5326,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121560208</v>
+        <v>121560204</v>
       </c>
       <c r="B41" t="n">
-        <v>94515</v>
+        <v>90746</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5337,31 +5338,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486785</v>
+        <v>486791</v>
       </c>
       <c r="R41" t="n">
-        <v>6779823</v>
+        <v>6779833</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -5108,10 +5108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121560193</v>
+        <v>121560208</v>
       </c>
       <c r="B39" t="n">
-        <v>92022</v>
+        <v>94515</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5120,30 +5120,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4368</v>
+        <v>2809</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5151,10 +5152,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486772</v>
+        <v>486785</v>
       </c>
       <c r="R39" t="n">
-        <v>6779917</v>
+        <v>6779823</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5187,11 +5188,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5219,10 +5215,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121560208</v>
+        <v>121560204</v>
       </c>
       <c r="B40" t="n">
-        <v>94515</v>
+        <v>90746</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5231,31 +5227,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5263,10 +5258,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486785</v>
+        <v>486791</v>
       </c>
       <c r="R40" t="n">
-        <v>6779823</v>
+        <v>6779833</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5326,10 +5321,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121560204</v>
+        <v>121560193</v>
       </c>
       <c r="B41" t="n">
-        <v>90746</v>
+        <v>92022</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5342,21 +5337,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5369,10 +5364,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486791</v>
+        <v>486772</v>
       </c>
       <c r="R41" t="n">
-        <v>6779833</v>
+        <v>6779917</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5405,6 +5400,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Flera mycel i området</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -2227,7 +2227,7 @@
         <v>119258774</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>119258953</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -795,11 +795,11 @@
         <v>119225230</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>92251</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4883,11 +4883,11 @@
         <v>119905244</v>
       </c>
       <c r="B37" t="n">
-        <v>91876</v>
+        <v>92251</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>119225230</v>
       </c>
       <c r="B3" t="n">
-        <v>92251</v>
+        <v>92254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>119258774</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>119258953</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>119905244</v>
       </c>
       <c r="B37" t="n">
-        <v>92251</v>
+        <v>92254</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>119225230</v>
       </c>
       <c r="B3" t="n">
-        <v>92254</v>
+        <v>92256</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>119905244</v>
       </c>
       <c r="B37" t="n">
-        <v>92254</v>
+        <v>92256</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>119225230</v>
       </c>
       <c r="B3" t="n">
-        <v>92256</v>
+        <v>92262</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>119905244</v>
       </c>
       <c r="B37" t="n">
-        <v>92256</v>
+        <v>92262</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>119225230</v>
       </c>
       <c r="B3" t="n">
-        <v>92265</v>
+        <v>92282</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>119905244</v>
       </c>
       <c r="B37" t="n">
-        <v>92265</v>
+        <v>92282</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>119225230</v>
       </c>
       <c r="B3" t="n">
-        <v>92282</v>
+        <v>92287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>119905244</v>
       </c>
       <c r="B37" t="n">
-        <v>92282</v>
+        <v>92287</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>119225230</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92289</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>119905244</v>
       </c>
       <c r="B37" t="n">
-        <v>92287</v>
+        <v>92289</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5430,6 +5430,118 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126199420</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58080</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Åberga, Åberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>486806</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6779915</v>
+      </c>
+      <c r="S42" t="n">
+        <v>50</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -5435,7 +5435,7 @@
         <v>126199420</v>
       </c>
       <c r="B42" t="n">
-        <v>58080</v>
+        <v>58084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -5537,7 +5537,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 30212-2024 artfynd.xlsx
+++ b/artfynd/A 30212-2024 artfynd.xlsx
@@ -5435,7 +5435,7 @@
         <v>126199420</v>
       </c>
       <c r="B42" t="n">
-        <v>58084</v>
+        <v>58087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
